--- a/stories/arbres/ATOM-TMP.JOU.001-06.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le jour, Fabien joue au jardin avec maman. Le soleil brille. Il fait chaud sur les mains. Maman dit : le jour, c'est le soleil. Fabien touche une pierre tiède. Parce que le soleil a chauffé. Le soir arrive. Le ciel devient bleu foncé. Fabien voit la lune. Il voit les étoiles. Maman dit : la nuit, c'est la lune. Ils rentrent. Fabien met son pyjama. Maman dit : la nuit, on fait dodo. Fabien se couche. Il ferme les yeux. Dodo la nuit. Le soleil le jour. La lune la nuit.</t>
+          <t>Le jour, Fabien joue au jardin avec maman. Le soleil brille. Il fait chaud sur les mains. Le jour, c'est le soleil. Fabien touche une pierre tiède. Parce que le soleil a chauffé. Le soir arrive. Le ciel devient bleu foncé. Fabien voit la lune. Il voit les étoiles. La nuit, c'est la lune. Ils rentrent. Fabien met son pyjama. La nuit, on fait dodo. Fabien se couche. Il ferme les yeux. Dodo la nuit. Le soleil le jour. La lune la nuit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le jour, Fabien joue au jardin avec maman. Le soleil brille. Il fait chaud sur les mains.
+maman|Le jour, c'est le soleil.
+narrateur|Fabien touche une pierre tiède. Parce que le soleil a chauffé. Le soir arrive. Le ciel devient bleu foncé. Fabien voit la lune. Il voit les étoiles.
+maman|La nuit, c'est la lune. Ils rentrent.
+narrateur|Fabien met son pyjama.
+maman|La nuit, on fait dodo.
+narrateur|Fabien se couche. Il ferme les yeux. Dodo la nuit. Le soleil le jour. La lune la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1496,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|La lune est là. Quel moment est-ce ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Fabien a vu le soleil le jour. Il a vu la lune la nuit. Il fait dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1836,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman baisse la lumière. Fabien respire.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2003,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2043,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.JOU.001-06.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 narrateur|Fabien se couche. Il ferme les yeux. Dodo la nuit. Le soleil le jour. La lune la nuit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1503,6 +1513,7 @@
           <t>narrateur|La lune est là. Quel moment est-ce ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1685,7 @@
           <t>narrateur|Fabien a vu le soleil le jour. Il a vu la lune la nuit. Il fait dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1841,6 +1853,7 @@
           <t>narrateur|Maman baisse la lumière. Fabien respire.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2008,6 +2021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2050,6 +2064,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2251,6 +2279,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.JOU.001-06.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fabien voit le soleil et la lune</t>
+          <t>La vache loin dans le pré</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Victorino veut aller voir la vache loin dans le pré. Le soleil chauffe l'herbe. La vache se cache. Ils la retrouvent. Le soir, la lune accroche le toit. Ils rentrent.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le jour, Fabien joue au jardin avec maman. Le soleil brille. Il fait chaud sur les mains. Le jour, c'est le soleil. Fabien touche une pierre tiède. Parce que le soleil a chauffé. Le soir arrive. Le ciel devient bleu foncé. Fabien voit la lune. Il voit les étoiles. La nuit, c'est la lune. Ils rentrent. Fabien met son pyjama. La nuit, on fait dodo. Fabien se couche. Il ferme les yeux. Dodo la nuit. Le soleil le jour. La lune la nuit.</t>
+          <t>Le pré sent le foin chaud. Une clôture de bois brûle un peu au soleil. Loin, une vache brune mange l'herbe. Victorino vit ici, avec maman. La maison est petite, au bord du pré. Un seau d'eau brille près du portail. Tu as vu la vache, là-bas ? Oui, maman. Je veux aller la voir. On marche dans le pré ? En ce moment, Victorino prend le seau. L'eau cliquette contre le métal. Ils passent le portail de bois. L'herbe est haute et tiède. Des insectes chantent dans les chardons. Le soleil chauffe le dos de Victorino. Le jour, c'est le soleil. Il est tout rond. Ils marchent vers la vache. Puis la vache disparaît derrière un buisson. Elle est partie ? Elle est derrière. On avance encore ? Victorino avance dans l'herbe. Une pierre tiède attend sous le pied. Il pose la main dessus. Le soleil l'a chauffée. Derrière le buisson, la vache lève la tête. Je la vois ! Bravo. Elle nous regarde. Victorino lève la main. La vache mâche, tout doucement. Une clochette sonne, très loin. Ils restent un moment. Le seau pèse un peu. On lui laisse de l'eau ? Victorino pose le seau près de la clôture. L'eau tremble au soleil. Le ciel change, tout doucement. Le pré devient plus bleu. Le soleil descend derrière le bois. Le jour s'en va. Victorino a froid aux mains. Ils reprennent le chemin du portail. Derrière eux, la vache est un point brun. Devant, la maison allume une fenêtre. Le ciel devient bleu foncé. Une lune ronde s'accroche au toit. La lune ! La nuit, c'est la lune. On rentre. Ils referment le portail. Le pré sent encore le foin, plus frais.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le jour, Fabien joue au jardin avec maman. Le &lt;emphasis level="moderate"&gt;soleil&lt;/emphasis&gt; brille. Il fait chaud sur les mains. Maman dit : le jour, c'est le soleil. Fabien touche une pierre tiède. Parce que le soleil a chauffé. Le soir arrive. Le ciel devient bleu foncé. Fabien voit la lune. Il voit les étoiles. Maman dit : la nuit, c'est la lune. Ils rentrent. Fabien met son pyjama. Maman dit : la nuit, on fait dodo. Fabien se couche. Il ferme les yeux. Dodo la nuit. Le soleil le jour. La lune la nuit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le pré sent le foin chaud. Une clôture de bois brûle un peu au soleil. Loin, une vache brune mange l'herbe. Victorino vit ici, avec maman. La maison est petite, au bord du pré. Un seau d'eau brille près du portail. Tu as vu la vache, là-bas ? Oui, maman. Je veux aller la voir. On marche dans le pré ? En ce moment, Victorino prend le seau. L'eau cliquette contre le métal. Ils passent le portail de bois. L'herbe est haute et tiède. Des insectes chantent dans les chardons. Le soleil chauffe le dos de Victorino. Le jour, c'est le soleil. Il est tout rond. Ils marchent vers la vache. Puis la vache disparaît derrière un buisson. Elle est partie ? Elle est derrière. On avance encore ? Victorino avance dans l'herbe. Une pierre tiède attend sous le pied. Il pose la main dessus. Le soleil l'a chauffée. Derrière le buisson, la vache lève la tête. Je la vois ! Bravo. Elle nous regarde. Victorino lève la main. La vache mâche, tout doucement. Une clochette sonne, très loin. Ils restent un moment. Le seau pèse un peu. On lui laisse de l'eau ? Victorino pose le seau près de la clôture. L'eau tremble au soleil. Le ciel change, tout doucement. Le pré devient plus bleu. Le soleil descend derrière le bois. Le jour s'en va. Victorino a froid aux mains. Ils reprennent le chemin du portail. Derrière eux, la vache est un point brun. Devant, la maison allume une fenêtre. Le ciel devient bleu foncé. Une lune ronde s'accroche au toit. La lune ! La nuit, c'est la lune. On rentre. Ils referment le portail. Le pré sent encore le foin, plus frais.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,13 +1324,60 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le jour, Fabien joue au jardin avec maman. Le soleil brille. Il fait chaud sur les mains.
+          <t>narrateur|Le pré sent le foin chaud.
+narrateur|Une clôture de bois brûle un peu au soleil.
+narrateur|Loin, une vache brune mange l'herbe.
+narrateur|Victorino vit ici, avec maman.
+narrateur|La maison est petite, au bord du pré.
+narrateur|Un seau d'eau brille près du portail.
+maman|Tu as vu la vache, là-bas ?
+enfant-m|Oui, maman.
+enfant-m|Je veux aller la voir.
+maman|On marche dans le pré ?
+narrateur|En ce moment, Victorino prend le seau.
+narrateur|L'eau cliquette contre le métal.
+narrateur|Ils passent le portail de bois.
+narrateur|L'herbe est haute et tiède.
+narrateur|Des insectes chantent dans les chardons.
+narrateur|Le soleil chauffe le dos de Victorino.
 maman|Le jour, c'est le soleil.
-narrateur|Fabien touche une pierre tiède. Parce que le soleil a chauffé. Le soir arrive. Le ciel devient bleu foncé. Fabien voit la lune. Il voit les étoiles.
-maman|La nuit, c'est la lune. Ils rentrent.
-narrateur|Fabien met son pyjama.
-maman|La nuit, on fait dodo.
-narrateur|Fabien se couche. Il ferme les yeux. Dodo la nuit. Le soleil le jour. La lune la nuit.</t>
+enfant-m|Il est tout rond.
+narrateur|Ils marchent vers la vache.
+narrateur|Puis la vache disparaît derrière un buisson.
+enfant-m|Elle est partie ?
+maman|Elle est derrière.
+maman|On avance encore ?
+narrateur|Victorino avance dans l'herbe.
+narrateur|Une pierre tiède attend sous le pied.
+narrateur|Il pose la main dessus.
+narrateur|Le soleil l'a chauffée.
+narrateur|Derrière le buisson, la vache lève la tête.
+enfant-m|Je la vois !
+maman|Bravo.
+maman|Elle nous regarde.
+narrateur|Victorino lève la main.
+narrateur|La vache mâche, tout doucement.
+narrateur|Une clochette sonne, très loin.
+narrateur|Ils restent un moment.
+narrateur|Le seau pèse un peu.
+maman|On lui laisse de l'eau ?
+narrateur|Victorino pose le seau près de la clôture.
+narrateur|L'eau tremble au soleil.
+narrateur|Le ciel change, tout doucement.
+narrateur|Le pré devient plus bleu.
+narrateur|Le soleil descend derrière le bois.
+maman|Le jour s'en va.
+narrateur|Victorino a froid aux mains.
+narrateur|Ils reprennent le chemin du portail.
+narrateur|Derrière eux, la vache est un point brun.
+narrateur|Devant, la maison allume une fenêtre.
+narrateur|Le ciel devient bleu foncé.
+narrateur|Une lune ronde s'accroche au toit.
+enfant-m|La lune !
+maman|La nuit, c'est la lune.
+maman|On rentre.
+narrateur|Ils referment le portail.
+narrateur|Le pré sent encore le foin, plus frais.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1350,12 +1409,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>La lune est là. Quel moment est-ce ?</t>
+          <t>La lune est accrochée au toit. Quel moment est-ce ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;lune&lt;/emphasis&gt; est là. Quel moment est-ce ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La lune est accrochée au toit. Quel moment est-ce ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1434,7 +1493,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1510,10 +1569,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|La lune est là. Quel moment est-ce ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|La lune est accrochée au toit.
+narrateur|Quel moment est-ce ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1538,12 +1597,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Fabien a vu le soleil le jour. Il a vu la lune la nuit. Il fait dodo la nuit.</t>
+          <t>Victorino pousse la porte de la maison. L'air dedans sent le pain. C'est la nuit. Oui. Le jour, le soleil. La nuit, la lune. Victorino enlève ses chaussures d'herbe. Des brins restent sur le paillasson. Il met son pyjama à pois. La nuit, on fait dodo. La vache aussi ? Elle mâche encore un peu. Puis elle dort dans le pré. Victorino grimpe dans le lit. La fenêtre montre encore la lune. Le pré est sombre, tout calme. Je l'ai vue. Oui. Au soleil, puis sous la lune. Il ferme un peu les yeux. Il revoit la clochette, très loin.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Fabien a vu le &lt;emphasis level="moderate"&gt;soleil&lt;/emphasis&gt; le jour. Il a vu la lune la nuit. Il fait dodo la nuit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino pousse la porte de la maison. L'air dedans sent le pain. C'est la nuit. Oui. Le jour, le soleil. La nuit, la lune. Victorino enlève ses chaussures d'herbe. Des brins restent sur le paillasson. Il met son pyjama à pois. La nuit, on fait dodo. La vache aussi ? Elle mâche encore un peu. Puis elle dort dans le pré. Victorino grimpe dans le lit. La fenêtre montre encore la lune. Le pré est sombre, tout calme. Je l'ai vue. Oui. Au soleil, puis sous la lune. Il ferme un peu les yeux. Il revoit la clochette, très loin.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1606,7 +1665,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1682,10 +1741,29 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Fabien a vu le soleil le jour. Il a vu la lune la nuit. Il fait dodo la nuit.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Victorino pousse la porte de la maison.
+narrateur|L'air dedans sent le pain.
+enfant-m|C'est la nuit.
+maman|Oui.
+maman|Le jour, le soleil.
+maman|La nuit, la lune.
+narrateur|Victorino enlève ses chaussures d'herbe.
+narrateur|Des brins restent sur le paillasson.
+narrateur|Il met son pyjama à pois.
+maman|La nuit, on fait dodo.
+enfant-m|La vache aussi ?
+maman|Elle mâche encore un peu.
+maman|Puis elle dort dans le pré.
+narrateur|Victorino grimpe dans le lit.
+narrateur|La fenêtre montre encore la lune.
+narrateur|Le pré est sombre, tout calme.
+enfant-m|Je l'ai vue.
+maman|Oui.
+maman|Au soleil, puis sous la lune.
+narrateur|Il ferme un peu les yeux.
+narrateur|Il revoit la clochette, très loin.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1710,12 +1788,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman baisse la lumière. Fabien respire.</t>
+          <t>Maman baisse la lumière. La chambre devient douce. Tu entends le pré ? Un peu. Un grillon commence, près de la clôture. Victorino respire, tout lentement. Ses mains sentent encore l'herbe.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman bais&lt;emphasis level="moderate"&gt;se&lt;/emphasis&gt; la lumière. Fabien respire.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman baisse la lumière. La chambre devient douce. Tu entends le pré ? Un peu. Un grillon commence, près de la clôture. Victorino respire, tout lentement. Ses mains sentent encore l'herbe.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1778,7 +1856,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1850,10 +1928,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman baisse la lumière. Fabien respire.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Maman baisse la lumière.
+narrateur|La chambre devient douce.
+maman|Tu entends le pré ?
+enfant-m|Un peu.
+narrateur|Un grillon commence, près de la clôture.
+narrateur|Victorino respire, tout lentement.
+narrateur|Ses mains sentent encore l'herbe.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1878,12 +1961,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Dehors, la lune tient le toit. La vache est un point brun, très loin. Le seau repose près de la clôture. Bonne nuit, vache. Bonne nuit. Le foin sent encore, tout frais.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Dehors, la lune tient le toit. La vache est un point brun, très loin. Le seau repose près de la clôture. Bonne nuit, vache. Bonne nuit. Le foin sent encore, tout frais.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1939,14 +2022,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2018,10 +2101,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Dehors, la lune tient le toit.
+narrateur|La vache est un point brun, très loin.
+narrateur|Le seau repose près de la clôture.
+enfant-m|Bonne nuit, vache.
+maman|Bonne nuit.
+narrateur|Le foin sent encore, tout frais.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2040,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2165,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.JOU.001-06.xlsx
+++ b/stories/arbres/ATOM-TMP.JOU.001-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin puis chambre</t>
+          <t>pré au bord de la maison, puis retour la nuit</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fabien, maman</t>
+          <t>Victorino, maman</t>
         </is>
       </c>
     </row>
